--- a/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
+++ b/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
@@ -2642,7 +2642,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationmaximumeffect</t>
+          <t>LanguageAcquisitionUkrainians_Integration_maximumeffect</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2652,7 +2652,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationaccessiblepopulation</t>
+          <t>LanguageAcquisitionUkrainians_Integration_accessiblepopulation</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2662,7 +2662,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationprobabilityofsuccess</t>
+          <t>LanguageAcquisitionUkrainians_Integration_probabilityofsuccess</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2672,7 +2672,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationsaturationpoint</t>
+          <t>LanguageAcquisitionUkrainians_Integration_saturationpoint</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2842,7 +2842,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_maximumeffect</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_maximumeffect</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2852,7 +2852,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_accessiblepopulation</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_accessiblepopulation</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2862,7 +2862,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_probabilityofsuccess</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_probabilityofsuccess</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2872,7 +2872,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_saturationpoint</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_saturationpoint</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3384,7 +3384,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration1</t>
+          <t>LanguageAcquisitionUkrainians_Integration_1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationsaturationpoint</t>
+          <t>LanguageAcquisitionUkrainians_Integration_saturationpoint</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration2</t>
+          <t>LanguageAcquisitionUkrainians_Integration_2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration1</t>
+          <t>LanguageAcquisitionUkrainians_Integration_1</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3426,17 +3426,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration3</t>
+          <t>LanguageAcquisitionUkrainians_Integration_3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration2</t>
+          <t>LanguageAcquisitionUkrainians_Integration_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationaccessiblepopulation</t>
+          <t>LanguageAcquisitionUkrainians_Integration_accessiblepopulation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3448,17 +3448,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration4</t>
+          <t>LanguageAcquisitionUkrainians_Integration_4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration3</t>
+          <t>LanguageAcquisitionUkrainians_Integration_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationprobabilityofsuccess</t>
+          <t>LanguageAcquisitionUkrainians_Integration_probabilityofsuccess</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integration4</t>
+          <t>LanguageAcquisitionUkrainians_Integration_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LanguageAcquisitionUkrainians_Integrationmaximumeffect</t>
+          <t>LanguageAcquisitionUkrainians_Integration_maximumeffect</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_1</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_saturationpoint</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_saturationpoint</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5144,12 +5144,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_2</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_1</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_1</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -5164,17 +5164,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_3</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_3</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_2</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_accessiblepopulation</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_accessiblepopulation</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5186,17 +5186,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_4</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_3</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_probabilityofsuccess</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_probabilityofsuccess</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_4</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SocialParticipationUkrainians_AccesToTransport_maximumeffect</t>
+          <t>SocialParticipationUkrainians_AccessToTransport_maximumeffect</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
